--- a/outputs/식이_최종반영_20260922/이전본_보관/보류삭제전/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/식이_최종반영_20260922/이전본_보관/보류삭제전/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R62720a755faa49fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R791a9cb8cf4b4224"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="Ra9875bb7fa0546be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="R3ac655f291994ef6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="R2e9e4a500e704869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Ra58bbe1551b64eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R1e707edf00464135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="R267476b28b5d42f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="R50a80d4509234cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="Rcc4e794c11a24b61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -526,8 +526,7 @@
         <x:v>225개 원문 추적·수정·보류·문구 ID·전문의 승인 필드</x:v>
       </x:c>
       <x:c r="C5" s="18" t="n">
-        <x:f>COUNTA(문구세트!G2:G395)</x:f>
-        <x:v>225</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -538,7 +537,6 @@
         <x:v>8축 · 회전 문항 · 답 3개</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
-        <x:f>COUNTA(축정의!B2:B100)</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -550,7 +548,6 @@
         <x:v>질환별 연결 축 · 금지 문구 (검수 7건 반영)</x:v>
       </x:c>
       <x:c r="C7" s="18" t="n">
-        <x:f>COUNTA(상병코드매핑!B2:B100)</x:f>
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -562,7 +559,6 @@
         <x:v>경계 · 창 · 시각 · 폭 · 스위치 · 임의값</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:f>COUNTA(설정값!B2:B100)</x:f>
         <x:v>52</x:v>
       </x:c>
     </x:row>
@@ -586,7 +582,6 @@
         <x:v>기획 후보. 전문의 승인 후 개인 조건 필터를 통과해야 노출</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:f>COUNTIF(문구세트!C2:C226,"사용")</x:f>
         <x:v>163</x:v>
       </x:c>
     </x:row>
@@ -598,7 +593,6 @@
         <x:v>축 적합성 · 단계 구분 확정 후 재검토</x:v>
       </x:c>
       <x:c r="C12" s="18" t="n">
-        <x:f>COUNTIF(문구세트!C2:C226,"보류")</x:f>
         <x:v>62</x:v>
       </x:c>
     </x:row>
